--- a/backend/data/financials_by_company/000728.SZ.xlsx
+++ b/backend/data/financials_by_company/000728.SZ.xlsx
@@ -3206,212 +3206,212 @@
       </c>
       <c r="DK1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="FA1" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Wei  Hu', 'age': 42, 'title': 'President &amp; Non-Independent Director', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kaiming  Si', 'age': 57, 'title': 'Chief Accountant', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Wei  Hu', 'age': 42, 'title': 'President &amp; Non-Independent Director', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kaiming  Si', 'age': 57, 'title': 'Chief Accountant', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Guo Wei  Zhang', 'age': 54, 'title': 'Chief Information Officer', 'yearBorn': 1971, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tangya  Lake', 'age': 52, 'title': 'Chief Risk Officer &amp; Compliance Director', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zhoufeng  Li', 'age': 44, 'title': 'Secretary of the Board of Directors', 'yearBorn': 1981, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ning  Chen', 'age': 41, 'title': 'Vice President', 'yearBorn': 1984, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Huabin  Liang', 'age': 42, 'title': 'Vice president', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -3516,34 +3516,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>7.03</v>
+        <v>7.57</v>
       </c>
       <c r="V2" t="n">
-        <v>7.22</v>
+        <v>7.5</v>
       </c>
       <c r="W2" t="n">
-        <v>7.01</v>
+        <v>7.44</v>
       </c>
       <c r="X2" t="n">
-        <v>7.39</v>
+        <v>7.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.03</v>
+        <v>7.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.22</v>
+        <v>7.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.01</v>
+        <v>7.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.39</v>
+        <v>7.65</v>
       </c>
       <c r="AC2" t="n">
         <v>0.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="AE2" t="n">
         <v>1782432000</v>
@@ -3552,37 +3552,37 @@
         <v>0.3396</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.597</v>
+        <v>0.589</v>
       </c>
       <c r="AI2" t="n">
-        <v>13.924529</v>
+        <v>14.207548</v>
       </c>
       <c r="AJ2" t="n">
-        <v>10.654425</v>
+        <v>10.870978</v>
       </c>
       <c r="AK2" t="n">
-        <v>67468949</v>
+        <v>50429553</v>
       </c>
       <c r="AL2" t="n">
-        <v>67468949</v>
+        <v>50429553</v>
       </c>
       <c r="AM2" t="n">
-        <v>34205011</v>
+        <v>43478007</v>
       </c>
       <c r="AN2" t="n">
-        <v>36146422</v>
+        <v>80725284</v>
       </c>
       <c r="AO2" t="n">
-        <v>36146422</v>
+        <v>80725284</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.38</v>
+        <v>7.53</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.39</v>
+        <v>7.54</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -3591,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>32204683264</v>
+        <v>32859248640</v>
       </c>
       <c r="AU2" t="n">
-        <v>30677358573</v>
+        <v>34168380886</v>
       </c>
       <c r="AV2" t="n">
         <v>6.66</v>
@@ -3609,19 +3609,19 @@
         <v>0.918299</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.3391576</v>
+        <v>5.4476767</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2778</v>
+        <v>7.2468</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.15245</v>
+        <v>8.087949999999999</v>
       </c>
       <c r="BC2" t="n">
         <v>0.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.025604552</v>
+        <v>0.023778072</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>47079809024</v>
+        <v>47734374400</v>
       </c>
       <c r="BH2" t="n">
         <v>0.3859</v>
@@ -3647,7 +3647,7 @@
         <v>0.5299499600000001</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.07362</v>
+        <v>0.0738</v>
       </c>
       <c r="BM2" t="n">
         <v>4363777891</v>
@@ -3656,7 +3656,7 @@
         <v>8.909000000000001</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.82837576</v>
+        <v>0.8452127</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -3688,13 +3688,13 @@
         <v>1495497600</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.805</v>
+        <v>7.914</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.078636944</v>
+        <v>-0.038119435</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CB2" t="n">
         <v>0.1</v>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>7.38</v>
+        <v>7.53</v>
       </c>
       <c r="CF2" t="n">
         <v>10.99</v>
@@ -3819,121 +3819,119 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>4.978661</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>GUOYUAN SECURITIES CO. LTD.</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="DL2" t="inlineStr">
         <is>
           <t>Guoyuan Securities Company Limited</t>
         </is>
       </c>
-      <c r="DP2" t="b">
+      <c r="DM2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DN2" t="n">
         <v>866424600000</v>
       </c>
+      <c r="DO2" t="n">
+        <v>-0.03999996</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>7.44 - 7.65</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
       <c r="DR2" t="n">
-        <v>0.3499999</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>7.01 - 7.39</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>34205011</v>
+        <v>43478007</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.87000036</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.13063069</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>6.66 - 10.13</t>
+        </is>
       </c>
       <c r="DV2" t="n">
-        <v>0.72000027</v>
+        <v>-2.6</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.10810815</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>6.66 - 10.13</t>
-        </is>
+        <v>-0.25666335</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-3.8119435</v>
       </c>
       <c r="DY2" t="n">
-        <v>-2.75</v>
+        <v>1745924340</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.27147087</v>
+        <v>1745924340</v>
       </c>
       <c r="EA2" t="n">
-        <v>-7.863694</v>
+        <v>1745996400</v>
       </c>
       <c r="EB2" t="n">
-        <v>1745924340</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1745924340</v>
+        <v>1745996400</v>
+      </c>
+      <c r="EC2" t="b">
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>1745996400</v>
+        <v>0.53</v>
       </c>
       <c r="EE2" t="n">
-        <v>1745996400</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
+        <v>0.69267</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.61924</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.53</v>
+        <v>12.160068</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.69267</v>
+        <v>-0.5284011</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.61924</v>
+        <v>7.53</v>
       </c>
       <c r="EJ2" t="n">
-        <v>11.917835</v>
+        <v>0.28320026</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.10220003</v>
+        <v>0.039079353</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.014042709</v>
+        <v>-0.55794954</v>
       </c>
       <c r="EM2" t="n">
-        <v>-0.7724495</v>
+        <v>-0.06898529</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0.0947506</v>
+        <v>15</v>
       </c>
       <c r="EO2" t="n">
         <v>15</v>
       </c>
-      <c r="EP2" t="n">
-        <v>15</v>
+      <c r="EP2" t="b">
+        <v>0</v>
       </c>
       <c r="EQ2" t="inlineStr">
         <is>
-          <t>[{'header': 'Dividend', 'message': '000728.SZ announced a cash dividend of CNY 0.10 with an ex-date of Jun. 26, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1782403200000, 'amount': '0.10'}}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="ER2" t="n">
-        <v>1782111897</v>
+        <v>1783062297</v>
       </c>
       <c r="ES2" t="inlineStr">
         <is>
@@ -3966,8 +3964,10 @@
       <c r="EY2" t="b">
         <v>0</v>
       </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
       </c>
       <c r="FA2" t="inlineStr"/>
     </row>
